--- a/branches/fix/table-width-json-blocks/StructureDefinition-preview-model.xlsx
+++ b/branches/fix/table-width-json-blocks/StructureDefinition-preview-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:07:59+00:00</t>
+    <t>2026-09-07T15:10:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/table-width-json-blocks/StructureDefinition-preview-model.xlsx
+++ b/branches/fix/table-width-json-blocks/StructureDefinition-preview-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:10:01+00:00</t>
+    <t>2026-09-07T15:18:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/table-width-json-blocks/StructureDefinition-preview-model.xlsx
+++ b/branches/fix/table-width-json-blocks/StructureDefinition-preview-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:18:56+00:00</t>
+    <t>2026-09-08T19:31:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
